--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6123-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6123-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC360E93-069C-4B2D-A12A-E91A49A2229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37D188BA-2A02-4494-8573-39B15900D7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{8FBA8063-5D79-46FB-94A7-904CB39209DD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{173025C1-2417-447D-A0F4-F8D74C8AE02C}"/>
   </bookViews>
   <sheets>
     <sheet name="6123-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1580,23 +1580,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F3098E-49EC-4009-BB0E-F8276C3C2D18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0020153A-A784-40E1-A838-8EFB2AC678EB}">
   <dimension ref="A1:R66"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1654,7 +1654,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1750,7 +1750,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2024</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>2023</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2022</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2021</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>26</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>26</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2020</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>8.4600000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>26</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>2019</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>26</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>26</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
         <v>26</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="44"/>
       <c r="B46" s="22" t="s">
         <v>65</v>
@@ -4052,7 +4052,7 @@
       <c r="Q46" s="48"/>
       <c r="R46" s="48"/>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2018</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>2017</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2016</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>2015</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>2014</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>2013</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>2012</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>2011</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>2010</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>2009</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>2008</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>2007</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <v>2006</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="41">
         <v>2004</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="39">
         <v>2003</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="41">
         <v>2002</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="39">
         <v>2001</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="41">
         <v>2000</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="39">
         <v>1999</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
         <v>66</v>
       </c>
